--- a/data/trans_camb/P16A11-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A11-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 10,28</t>
+          <t>0,99; 10,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 5,6</t>
+          <t>-2,48; 5,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 13,72</t>
+          <t>5,25; 14,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 4,06</t>
+          <t>-5,82; 3,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 4,44</t>
+          <t>-5,42; 4,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 5,26</t>
+          <t>-3,0; 5,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 6,47</t>
+          <t>-0,61; 6,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 4,01</t>
+          <t>-2,33; 4,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,55</t>
+          <t>2,62; 8,59</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 113,33</t>
+          <t>6,43; 114,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 62,97</t>
+          <t>-19,88; 64,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,59; 158,1</t>
+          <t>38,46; 156,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,28; 58,23</t>
+          <t>-49,68; 51,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,06; 60,88</t>
+          <t>-45,89; 56,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 70,97</t>
+          <t>-22,79; 69,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 72,04</t>
+          <t>-5,09; 67,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 45,43</t>
+          <t>-19,66; 44,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,56; 95,42</t>
+          <t>20,85; 94,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 5,33</t>
+          <t>-4,55; 5,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 6,16</t>
+          <t>-4,0; 6,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 12,75</t>
+          <t>2,98; 13,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 8,62</t>
+          <t>-0,51; 8,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 5,86</t>
+          <t>-2,46; 5,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 10,05</t>
+          <t>2,92; 10,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 5,41</t>
+          <t>-0,8; 5,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 4,66</t>
+          <t>-1,65; 4,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,56</t>
+          <t>4,57; 10,78</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 48,78</t>
+          <t>-28,82; 59,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 58,76</t>
+          <t>-24,64; 63,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,65; 130,28</t>
+          <t>18,81; 126,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 217,38</t>
+          <t>-10,87; 214,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 147,71</t>
+          <t>-35,67; 136,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,84; 265,74</t>
+          <t>34,98; 262,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 69,82</t>
+          <t>-7,36; 76,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 61,19</t>
+          <t>-14,74; 58,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,46; 135,14</t>
+          <t>39,49; 139,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 13,67</t>
+          <t>4,91; 13,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 8,45</t>
+          <t>0,03; 8,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 10,82</t>
+          <t>-7,97; 11,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 15,94</t>
+          <t>1,18; 15,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 15,97</t>
+          <t>-1,48; 16,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 16,64</t>
+          <t>1,51; 16,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 13,28</t>
+          <t>5,4; 13,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 8,92</t>
+          <t>1,22; 8,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 10,75</t>
+          <t>-7,74; 10,38</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,6; 137,08</t>
+          <t>34,96; 138,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 86,78</t>
+          <t>0,23; 83,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,42; 96,9</t>
+          <t>-59,26; 103,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,78; 156,29</t>
+          <t>5,18; 145,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 146,96</t>
+          <t>-9,9; 160,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,39; 160,04</t>
+          <t>4,71; 152,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,15; 126,14</t>
+          <t>39,42; 130,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,25; 81,52</t>
+          <t>7,92; 80,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-48,46; 92,17</t>
+          <t>-53,84; 88,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 5,37</t>
+          <t>-0,86; 5,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 4,46</t>
+          <t>-1,51; 4,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,67; 8,29</t>
+          <t>2,18; 8,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 0,37</t>
+          <t>-6,52; 0,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 0,47</t>
+          <t>-6,5; 0,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 50,96</t>
+          <t>0,55; 51,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,13</t>
+          <t>-2,36; 2,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,59</t>
+          <t>-2,69; 1,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 35,04</t>
+          <t>2,76; 36,59</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 35,09</t>
+          <t>-5,28; 37,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 29,48</t>
+          <t>-8,52; 29,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,4; 56,34</t>
+          <t>12,58; 54,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 3,73</t>
+          <t>-40,32; 4,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,28; 4,19</t>
+          <t>-42,13; 1,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,69; 420,63</t>
+          <t>4,43; 385,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 14,3</t>
+          <t>-14,26; 17,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 10,73</t>
+          <t>-16,46; 13,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,86; 228,44</t>
+          <t>17,55; 250,9</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,14</t>
+          <t>1,51; 11,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 9,78</t>
+          <t>0,35; 9,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,15; 12,67</t>
+          <t>2,78; 12,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,47; 14,91</t>
+          <t>6,45; 14,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 9,23</t>
+          <t>0,75; 9,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,55; 14,98</t>
+          <t>3,24; 15,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,51; 11,91</t>
+          <t>5,51; 11,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,71</t>
+          <t>1,57; 7,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,0; 12,82</t>
+          <t>4,65; 12,58</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,65; 118,89</t>
+          <t>9,29; 116,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,4; 105,45</t>
+          <t>1,42; 101,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19,22; 132,28</t>
+          <t>19,85; 133,3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37,68; 121,0</t>
+          <t>37,88; 120,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,34; 75,79</t>
+          <t>4,46; 77,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,21; 116,94</t>
+          <t>20,9; 119,04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,51; 100,62</t>
+          <t>34,77; 100,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,87; 64,81</t>
+          <t>10,08; 64,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>33,25; 108,04</t>
+          <t>29,98; 105,94</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,99</t>
+          <t>-1,98; 1,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,07</t>
+          <t>-2,88; 0,1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,51</t>
+          <t>-2,35; 1,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,28; 10,82</t>
+          <t>3,51; 10,57</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 6,72</t>
+          <t>-1,27; 6,76</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,42; 8,59</t>
+          <t>1,48; 8,72</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,62; 8,98</t>
+          <t>2,46; 8,81</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,84</t>
+          <t>-1,24; 5,05</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 5,53</t>
+          <t>-0,62; 5,6</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-84,01; 307,15</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 410,22</t>
-        </is>
-      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,3; 287,47</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12,18; 45,32</t>
+          <t>12,78; 46,61</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 28,83</t>
+          <t>-4,74; 29,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,26; 37,72</t>
+          <t>5,3; 38,6</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,6; 47,97</t>
+          <t>11,52; 46,77</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 25,65</t>
+          <t>-5,98; 27,02</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 29,66</t>
+          <t>-3,02; 29,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,83</t>
+          <t>2,21; 5,94</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,02</t>
+          <t>0,63; 3,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,04; 7,38</t>
+          <t>1,12; 7,46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,19</t>
+          <t>2,25; 5,98</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,9</t>
+          <t>-0,95; 2,95</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,23; 22,6</t>
+          <t>3,06; 23,51</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,33</t>
+          <t>2,9; 5,54</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,9</t>
+          <t>0,2; 2,84</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,75; 15,48</t>
+          <t>3,88; 14,32</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>16,34; 49,35</t>
+          <t>16,0; 49,54</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4,73; 33,83</t>
+          <t>4,68; 32,86</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8,27; 61,34</t>
+          <t>9,87; 62,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14,34; 39,43</t>
+          <t>12,63; 38,5</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 18,11</t>
+          <t>-5,43; 18,94</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,06; 137,39</t>
+          <t>18,01; 147,38</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,87; 37,86</t>
+          <t>19,02; 39,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,94; 20,58</t>
+          <t>1,23; 20,18</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25,48; 108,06</t>
+          <t>25,97; 102,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A11-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A11-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,64</t>
+          <t>9,11</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>5,78</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 10,47</t>
+          <t>1,16; 10,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 5,93</t>
+          <t>-2,73; 6,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 14,13</t>
+          <t>4,5; 13,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 3,87</t>
+          <t>-5,84; 4,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 4,1</t>
+          <t>-5,74; 4,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 5,14</t>
+          <t>-2,46; 6,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 6,54</t>
+          <t>-0,64; 6,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 4,01</t>
+          <t>-2,32; 4,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 8,59</t>
+          <t>2,65; 8,73</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 114,81</t>
+          <t>8,91; 117,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 64,99</t>
+          <t>-22,16; 69,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,46; 156,84</t>
+          <t>32,53; 151,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,68; 51,94</t>
+          <t>-47,19; 55,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,89; 56,39</t>
+          <t>-46,04; 60,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 69,56</t>
+          <t>-19,33; 83,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 67,94</t>
+          <t>-5,1; 71,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 44,38</t>
+          <t>-20,46; 47,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,85; 94,33</t>
+          <t>20,66; 97,99</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,76</t>
+          <t>7,85</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>7,46</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,6</t>
+          <t>7,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 5,9</t>
+          <t>-4,63; 4,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 6,66</t>
+          <t>-3,78; 6,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 13,05</t>
+          <t>2,91; 12,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 8,38</t>
+          <t>-0,03; 8,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 5,43</t>
+          <t>-1,76; 6,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 10,36</t>
+          <t>3,79; 11,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,62</t>
+          <t>-1,21; 5,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,59</t>
+          <t>-1,76; 4,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,57; 10,78</t>
+          <t>4,82; 11,1</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>117,23%</t>
+          <t>130,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,82; 59,4</t>
+          <t>-30,72; 45,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,64; 63,35</t>
+          <t>-25,25; 64,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,81; 126,96</t>
+          <t>15,28; 119,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 214,93</t>
+          <t>-3,79; 207,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 136,7</t>
+          <t>-28,38; 146,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,98; 262,84</t>
+          <t>39,36; 282,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 76,25</t>
+          <t>-11,32; 68,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 58,74</t>
+          <t>-16,59; 59,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,49; 139,84</t>
+          <t>43,06; 142,4</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>8,81</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,3</t>
+          <t>9,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>9,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 13,85</t>
+          <t>5,47; 13,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 8,34</t>
+          <t>0,04; 8,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 11,19</t>
+          <t>4,42; 13,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 15,42</t>
+          <t>1,15; 16,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 16,81</t>
+          <t>-1,72; 15,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 16,47</t>
+          <t>1,64; 15,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 13,21</t>
+          <t>5,59; 12,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 8,57</t>
+          <t>1,42; 8,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 10,38</t>
+          <t>5,72; 12,5</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,96; 138,14</t>
+          <t>36,81; 138,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 83,1</t>
+          <t>0,02; 84,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,26; 103,16</t>
+          <t>30,44; 131,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 145,41</t>
+          <t>3,99; 156,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 160,05</t>
+          <t>-12,04; 160,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,71; 152,8</t>
+          <t>8,57; 165,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,42; 130,16</t>
+          <t>39,81; 120,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,92; 80,84</t>
+          <t>9,87; 86,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,84; 88,28</t>
+          <t>38,79; 116,93</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>4,67</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,49</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,69</t>
+          <t>3,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 5,68</t>
+          <t>-1,06; 5,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,46</t>
+          <t>-1,69; 4,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,2</t>
+          <t>1,59; 7,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 0,42</t>
+          <t>-6,31; 0,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 0,18</t>
+          <t>-6,19; 0,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 51,81</t>
+          <t>-1,45; 4,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,49</t>
+          <t>-2,46; 2,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,88</t>
+          <t>-2,8; 1,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 36,59</t>
+          <t>0,76; 5,4</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>140,61%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 37,95</t>
+          <t>-6,22; 35,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 29,64</t>
+          <t>-9,51; 31,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,58; 54,71</t>
+          <t>8,38; 52,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,32; 4,03</t>
+          <t>-41,01; 2,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,13; 1,78</t>
+          <t>-40,34; 5,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,43; 385,86</t>
+          <t>-9,56; 40,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 17,33</t>
+          <t>-14,78; 15,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 13,28</t>
+          <t>-16,97; 12,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,55; 250,9</t>
+          <t>4,29; 37,86</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,75</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>12,18</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,26</t>
+          <t>9,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 11,2</t>
+          <t>1,49; 11,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 9,44</t>
+          <t>0,3; 9,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,78; 12,77</t>
+          <t>1,49; 10,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,45; 14,79</t>
+          <t>5,87; 14,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 9,58</t>
+          <t>0,38; 9,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,24; 15,17</t>
+          <t>8,41; 16,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,51; 11,98</t>
+          <t>5,36; 11,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,85</t>
+          <t>1,59; 7,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,65; 12,58</t>
+          <t>6,37; 12,3</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,29; 116,59</t>
+          <t>7,66; 117,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1,42; 101,84</t>
+          <t>1,3; 97,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19,85; 133,3</t>
+          <t>9,84; 113,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37,88; 120,93</t>
+          <t>33,74; 120,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,46; 77,63</t>
+          <t>3,73; 75,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,9; 119,04</t>
+          <t>47,17; 130,75</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,77; 100,41</t>
+          <t>35,67; 100,27</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10,08; 64,47</t>
+          <t>10,52; 64,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>29,98; 105,94</t>
+          <t>42,8; 104,12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,87</t>
+          <t>4,12</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>2,51</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,96</t>
+          <t>-1,98; 2,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,1</t>
+          <t>-2,91; 0,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,36</t>
+          <t>-2,12; 1,51</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,51; 10,57</t>
+          <t>3,53; 10,85</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 6,76</t>
+          <t>-0,8; 6,86</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,72</t>
+          <t>0,4; 7,37</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,81</t>
+          <t>2,19; 8,71</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 5,05</t>
+          <t>-1,37; 4,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,6</t>
+          <t>-0,29; 5,69</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-24,3%</t>
+          <t>-24,74%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-84,01; 307,15</t>
+          <t>-83,42; 444,38</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-88,3; 287,47</t>
+          <t>-86,98; 314,54</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12,78; 46,61</t>
+          <t>13,65; 47,71</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 29,36</t>
+          <t>-2,96; 30,3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,3; 38,6</t>
+          <t>1,38; 31,86</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,52; 46,77</t>
+          <t>10,43; 46,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 27,02</t>
+          <t>-6,61; 25,45</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 29,05</t>
+          <t>-1,27; 30,43</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>6,33</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,31</t>
+          <t>4,1</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>5,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,94</t>
+          <t>2,26; 5,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,92</t>
+          <t>0,39; 3,95</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,12; 7,46</t>
+          <t>4,51; 7,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,98</t>
+          <t>2,45; 6,26</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,95</t>
+          <t>-0,73; 3,35</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,06; 23,51</t>
+          <t>2,32; 5,69</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,54</t>
+          <t>2,89; 5,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,84</t>
+          <t>0,39; 2,97</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,88; 14,32</t>
+          <t>4,03; 6,33</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>16,0; 49,54</t>
+          <t>17,21; 47,99</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4,68; 32,86</t>
+          <t>2,84; 33,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9,87; 62,45</t>
+          <t>32,78; 67,08</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12,63; 38,5</t>
+          <t>13,71; 39,82</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 18,94</t>
+          <t>-4,25; 20,89</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,01; 147,38</t>
+          <t>13,05; 36,08</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,02; 39,53</t>
+          <t>18,83; 38,05</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,23; 20,18</t>
+          <t>2,4; 20,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25,97; 102,3</t>
+          <t>25,78; 44,53</t>
         </is>
       </c>
     </row>
